--- a/R_analysis/output/tables/Tabela_IVS_estratos.xlsx
+++ b/R_analysis/output/tables/Tabela_IVS_estratos.xlsx
@@ -409,12 +409,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Muito baixa</t>
+          <t>Very low</t>
         </is>
       </c>
       <c r="C2">
@@ -445,12 +445,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Baixa</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="C3">
@@ -481,12 +481,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="C4">
@@ -517,12 +517,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>High</t>
         </is>
       </c>
       <c r="C5">
@@ -553,12 +553,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Muito baixa</t>
+          <t>Very low</t>
         </is>
       </c>
       <c r="C6">
@@ -589,12 +589,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Baixa</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="C7">
@@ -625,12 +625,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="C8">
@@ -661,12 +661,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>High</t>
         </is>
       </c>
       <c r="C9">
